--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484600_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484600_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5054</v>
+        <v>5.2276</v>
       </c>
       <c r="E2" t="n">
-        <v>7.018</v>
+        <v>7.087</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5126</v>
+        <v>-1.8594</v>
       </c>
       <c r="G2" t="n">
         <v>1.3846</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0961</v>
+        <v>1.8183</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5543</v>
+        <v>1.6233</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5417</v>
+        <v>0.1949</v>
       </c>
       <c r="V2" t="n">
         <v>0.5587</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2078</v>
+        <v>3.4203</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2368</v>
+        <v>3.6734</v>
       </c>
       <c r="F3" t="n">
-        <v>1.971</v>
+        <v>-0.2531</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5907</v>
+        <v>3.7419</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6465</v>
+        <v>2.588</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2372</v>
+        <v>1.1538</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9719</v>
+        <v>2.7835</v>
       </c>
       <c r="K3" t="n">
-        <v>0.201</v>
+        <v>2.7835</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1729</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3813</v>
+        <v>0.9584</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4456</v>
+        <v>-0.1955</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0643</v>
+        <v>1.1538</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R3" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7792</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2142</v>
+        <v>0.7225</v>
       </c>
       <c r="U3" t="n">
-        <v>1.565</v>
+        <v>0.0109</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2026</v>
+        <v>-0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9109</v>
+        <v>1.267</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7083</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6071</v>
+        <v>2.4675</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8107</v>
+        <v>1.2892</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2036</v>
+        <v>1.1783</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7419</v>
+        <v>-0.5907</v>
       </c>
       <c r="H4" t="n">
-        <v>2.588</v>
+        <v>0.6465</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1538</v>
+        <v>-1.2372</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7835</v>
+        <v>-0.9719</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7835</v>
+        <v>0.201</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.1729</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9584</v>
+        <v>0.3813</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1955</v>
+        <v>0.4456</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1538</v>
+        <v>-0.0643</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9202</v>
+        <v>2.0388</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8597</v>
+        <v>1.2666</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0605</v>
+        <v>0.7722</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3219</v>
+        <v>1.2026</v>
       </c>
       <c r="W4" t="n">
-        <v>1.267</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5889</v>
+        <v>-0.7083</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1276</v>
+        <v>0.3779</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7845</v>
+        <v>-0.6333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9121</v>
+        <v>1.0112</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4515</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.044</v>
+        <v>0.2063</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1652</v>
+        <v>-0.0139</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1211</v>
+        <v>0.2202</v>
       </c>
       <c r="V5" t="n">
         <v>0.6231</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2935</v>
+        <v>-0.4131</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8519</v>
+        <v>-0.8602</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1454</v>
+        <v>0.4472</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7861</v>
+        <v>-0.2891</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1374</v>
+        <v>0.1789</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9235</v>
+        <v>-0.468</v>
       </c>
       <c r="J6" t="n">
-        <v>0.637</v>
+        <v>-0.3743</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4703</v>
+        <v>0.1576</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1667</v>
+        <v>-0.5319</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4231</v>
+        <v>0.0852</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3329</v>
+        <v>0.0213</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0902</v>
+        <v>0.064</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5656</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8484</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3252</v>
+        <v>0.142</v>
       </c>
       <c r="T6" t="n">
-        <v>4.7414</v>
+        <v>0.1267</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4162</v>
+        <v>0.0153</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.267</v>
+        <v>-0.999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>-0.6127</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5889</v>
+        <v>-0.3863</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3117</v>
+        <v>-1.6006</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6845</v>
+        <v>-0.9008</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3728</v>
+        <v>-0.6997</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2891</v>
+        <v>-0.1826</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1789</v>
+        <v>0.202</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.468</v>
+        <v>-0.3846</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3743</v>
+        <v>-0.5977</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1576</v>
+        <v>0.0433</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5319</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0852</v>
+        <v>0.4151</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0213</v>
+        <v>0.1587</v>
       </c>
       <c r="O7" t="n">
-        <v>0.064</v>
+        <v>0.2564</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.582</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6976</v>
+        <v>0.6131</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0591</v>
+        <v>-0.0311</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.999</v>
+        <v>-1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6127</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3863</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8287</v>
+        <v>-2.6935</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2032</v>
+        <v>-2.9834</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6254</v>
+        <v>0.2899</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1826</v>
+        <v>-1.855</v>
       </c>
       <c r="H8" t="n">
-        <v>0.202</v>
+        <v>-2.3551</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3846</v>
+        <v>0.5001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5977</v>
+        <v>-1.1222</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0433</v>
+        <v>-1.1737</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.641</v>
+        <v>0.0515</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4151</v>
+        <v>-0.7329</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1587</v>
+        <v>-1.1815</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2564</v>
+        <v>0.4486</v>
       </c>
       <c r="P8" t="n">
         <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3539</v>
+        <v>-0.1054</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3107</v>
+        <v>0.1546</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0432</v>
+        <v>-0.26</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3998</v>
+        <v>-2.8172</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6154</v>
+        <v>-3.279</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2156</v>
+        <v>0.4618</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.855</v>
+        <v>-5.5287</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3551</v>
+        <v>-4.0993</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5001</v>
+        <v>-1.4294</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1222</v>
+        <v>-5.4351</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1737</v>
+        <v>-3.5893</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0515</v>
+        <v>-1.8458</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7329</v>
+        <v>-0.0935</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1815</v>
+        <v>-0.51</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4486</v>
+        <v>0.4164</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8117</v>
+        <v>0.6827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4774</v>
+        <v>0.7217</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3343</v>
+        <v>-0.0391</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.212</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4909</v>
+        <v>-2.8558</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6802</v>
+        <v>-0.9087</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1893</v>
+        <v>-1.9472</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.5287</v>
+        <v>-0.7861</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.0993</v>
+        <v>0.1374</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4294</v>
+        <v>-0.9235</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.4351</v>
+        <v>0.637</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.5893</v>
+        <v>0.4703</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8458</v>
+        <v>0.1667</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0935</v>
+        <v>-1.4231</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.51</v>
+        <v>-0.3329</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4164</v>
+        <v>-1.0902</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0995</v>
+        <v>-3.8484</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.991</v>
+        <v>1.7628</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6795</v>
+        <v>1.9808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3116</v>
+        <v>-0.218</v>
       </c>
       <c r="V10" t="n">
-        <v>2.212</v>
+        <v>-1.267</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7374</v>
+        <v>-4.3979</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2778</v>
+        <v>-3.6218</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4597</v>
+        <v>-0.7761</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6992</v>
+        <v>-3.8054</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1795</v>
+        <v>-1.0584</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5197</v>
+        <v>-2.747</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7468</v>
+        <v>-2.4574</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8302</v>
+        <v>-0.576</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0833</v>
+        <v>-1.8814</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9523</v>
+        <v>-1.348</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3493</v>
+        <v>-0.4824</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.603</v>
+        <v>-0.8656</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6309</v>
+        <v>0.096</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5294</v>
+        <v>-0.2481</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1014</v>
+        <v>0.3441</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3863</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9288</v>
+        <v>-4.7919</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9793</v>
+        <v>-3.4561</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9495</v>
+        <v>-1.3358</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8054</v>
+        <v>-3.6992</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0584</v>
+        <v>-2.1795</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.747</v>
+        <v>-1.5197</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4574</v>
+        <v>-0.7468</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.576</v>
+        <v>-0.8302</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8814</v>
+        <v>0.0833</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.348</v>
+        <v>-2.9523</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4824</v>
+        <v>-1.3493</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8656</v>
+        <v>-1.603</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4349</v>
+        <v>0.5764</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6056</v>
+        <v>0.3511</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1707</v>
+        <v>0.2253</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>-0.3863</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>-0.07480000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.889200000000001</v>
+        <v>-6.9789</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6908</v>
+        <v>-5.0283</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1984</v>
+        <v>-1.9506</v>
       </c>
       <c r="G13" t="n">
         <v>-6.9415</v>
@@ -1468,13 +1468,13 @@
         <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6501</v>
+        <v>0.2602</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.193</v>
+        <v>0.4695</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.457</v>
+        <v>-0.2093</v>
       </c>
       <c r="V13" t="n">
         <v>1.5349</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.4321</v>
+        <v>-15.0556</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.9983</v>
+        <v>-9.622</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.4338</v>
+        <v>-5.4335</v>
       </c>
       <c r="G14" t="n">
         <v>-19.0033</v>
@@ -1522,13 +1522,13 @@
         <v>-9.2233</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.898300000000001</v>
+        <v>-4.8983</v>
       </c>
       <c r="L14" t="n">
         <v>-4.325</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.7798</v>
+        <v>-9.779800000000002</v>
       </c>
       <c r="N14" t="n">
         <v>-6.7323</v>
@@ -1546,10 +1546,10 @@
         <v>10.9955</v>
       </c>
       <c r="S14" t="n">
-        <v>7.417199999999998</v>
+        <v>8.7935</v>
       </c>
       <c r="T14" t="n">
-        <v>6.391399999999999</v>
+        <v>7.767899999999999</v>
       </c>
       <c r="U14" t="n">
         <v>1.0254</v>
@@ -1561,13 +1561,13 @@
         <v>9.242700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.674600000000001</v>
+        <v>-7.6746</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5058</v>
+        <v>6.2345</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0388</v>
+        <v>4.5262</v>
       </c>
       <c r="F15" t="n">
-        <v>3.467</v>
+        <v>1.7083</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3786</v>
+        <v>5.3314</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8493</v>
+        <v>3.081</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5293</v>
+        <v>2.2504</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6769</v>
+        <v>3.8343</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2755</v>
+        <v>2.4492</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4014</v>
+        <v>1.3851</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7017</v>
+        <v>1.4971</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5738</v>
+        <v>0.6318</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1279</v>
+        <v>0.8653</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2235</v>
+        <v>-0.0132</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1666</v>
+        <v>0.0585</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0568</v>
+        <v>-0.0717</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2774</v>
+        <v>0.6335</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8528</v>
+        <v>6.2128</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0455</v>
+        <v>3.0388</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8074</v>
+        <v>3.1741</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3314</v>
+        <v>5.3786</v>
       </c>
       <c r="H16" t="n">
-        <v>3.081</v>
+        <v>1.8493</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2504</v>
+        <v>3.5293</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8343</v>
+        <v>4.6769</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4492</v>
+        <v>1.2755</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3851</v>
+        <v>3.4014</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4971</v>
+        <v>0.7017</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6318</v>
+        <v>0.5738</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8653</v>
+        <v>0.1279</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9163</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3949</v>
+        <v>-0.5164</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4223</v>
+        <v>-0.1666</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0274</v>
+        <v>-0.3498</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6335</v>
+        <v>1.2774</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6335</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3304</v>
+        <v>4.208</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0828</v>
+        <v>1.5059</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2475</v>
+        <v>2.7021</v>
       </c>
       <c r="G17" t="n">
         <v>1.4991</v>
@@ -1780,13 +1780,13 @@
         <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.352</v>
+        <v>-1.4744</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1622</v>
+        <v>-0.4148</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5142</v>
+        <v>-1.0596</v>
       </c>
       <c r="V17" t="n">
         <v>2.5339</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.317</v>
+        <v>1.9858</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8192</v>
+        <v>0.7129</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1362</v>
+        <v>1.2729</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2356</v>
+        <v>3.9403</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7134</v>
+        <v>3.5652</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4778</v>
+        <v>0.3751</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3222</v>
+        <v>2.7258</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7743</v>
+        <v>2.6068</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5478</v>
+        <v>0.119</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0866</v>
+        <v>1.2145</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0609</v>
+        <v>0.9584</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0256</v>
+        <v>0.2561</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5526</v>
+        <v>-1.4334</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0973</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4552</v>
+        <v>-0.8633</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>2.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1014</v>
+        <v>1.0534</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3283</v>
+        <v>0.9101</v>
       </c>
       <c r="F19" t="n">
-        <v>0.773</v>
+        <v>0.1433</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9403</v>
+        <v>1.5278</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5652</v>
+        <v>-0.4404</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3751</v>
+        <v>1.9682</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7258</v>
+        <v>0.8976</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6068</v>
+        <v>-0.4617</v>
       </c>
       <c r="L19" t="n">
-        <v>0.119</v>
+        <v>1.3593</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2145</v>
+        <v>0.6302</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9584</v>
+        <v>0.0213</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2561</v>
+        <v>0.6089</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3179</v>
+        <v>-0.4902</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9547</v>
+        <v>0.0125</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3631</v>
+        <v>-0.5027</v>
       </c>
       <c r="V19" t="n">
-        <v>0.945</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2774</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4757</v>
+        <v>0.7089</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.7054</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.422</v>
+        <v>0.0034</v>
       </c>
       <c r="G20" t="n">
         <v>2.2594</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.433</v>
+        <v>-1.1999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1847</v>
+        <v>-0.3771</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2483</v>
+        <v>-0.8228</v>
       </c>
       <c r="V20" t="n">
         <v>-1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.4336</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1374</v>
+        <v>-0.5605</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2375</v>
+        <v>0.9941</v>
       </c>
       <c r="G21" t="n">
         <v>0.8962</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5396</v>
+        <v>-0.2061</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6976</v>
+        <v>-0.1206</v>
       </c>
       <c r="U21" t="n">
-        <v>0.158</v>
+        <v>-0.0854</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6231</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0044</v>
+        <v>0.3883</v>
       </c>
       <c r="E22" t="n">
-        <v>0.237</v>
+        <v>-1.2061</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2326</v>
+        <v>1.5944</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5278</v>
+        <v>-0.5898</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4404</v>
+        <v>-0.439</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9682</v>
+        <v>-0.1508</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8976</v>
+        <v>-1.6213</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4617</v>
+        <v>-1.022</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3593</v>
+        <v>-0.5994</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6302</v>
+        <v>1.0315</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0213</v>
+        <v>0.583</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6089</v>
+        <v>0.4486</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5392</v>
+        <v>-0.0273</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6606</v>
+        <v>0.4152</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8786</v>
+        <v>-0.4425</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0036</v>
+        <v>0.2548</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4946</v>
+        <v>-1.5884</v>
       </c>
       <c r="F23" t="n">
-        <v>1.491</v>
+        <v>1.8432</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5898</v>
+        <v>-0.2356</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.439</v>
+        <v>-0.7134</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1508</v>
+        <v>0.4778</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6213</v>
+        <v>-1.3222</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.022</v>
+        <v>-0.7743</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5994</v>
+        <v>-0.5478</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0315</v>
+        <v>1.0866</v>
       </c>
       <c r="N23" t="n">
-        <v>0.583</v>
+        <v>0.0609</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4486</v>
+        <v>1.0256</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4192</v>
+        <v>0.4904</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1267</v>
+        <v>0.3281</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5459000000000001</v>
+        <v>0.1623</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.297</v>
+        <v>-0.3465</v>
       </c>
       <c r="E24" t="n">
         <v>0.01</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3069</v>
+        <v>-0.3565</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4006</v>
@@ -2326,13 +2326,13 @@
         <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0692</v>
+        <v>-0.1188</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0142</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.0104</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0273</v>
+        <v>-0.9282</v>
       </c>
       <c r="E25" t="n">
         <v>-1.5177</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4903</v>
+        <v>0.5894</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0669</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3374</v>
+        <v>-0.2383</v>
       </c>
       <c r="T25" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0621</v>
+        <v>0.0369</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6231</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9276</v>
+        <v>-2.4914</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2375</v>
+        <v>-1.1029</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6901</v>
+        <v>-1.3885</v>
       </c>
       <c r="G26" t="n">
         <v>-0.5369</v>
@@ -2482,13 +2482,13 @@
         <v>2.3823</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3437</v>
+        <v>-0.9074</v>
       </c>
       <c r="T26" t="n">
-        <v>1.0053</v>
+        <v>0.1399</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.349</v>
+        <v>-1.0473</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5131</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>16.432</v>
+        <v>17.714</v>
       </c>
       <c r="E27" t="n">
-        <v>5.433699999999999</v>
+        <v>5.4337</v>
       </c>
       <c r="F27" t="n">
-        <v>10.9983</v>
+        <v>12.2802</v>
       </c>
       <c r="G27" t="n">
         <v>19.003</v>
@@ -2533,19 +2533,19 @@
         <v>7.3725</v>
       </c>
       <c r="J27" t="n">
-        <v>9.779699999999998</v>
+        <v>9.779699999999997</v>
       </c>
       <c r="K27" t="n">
-        <v>6.7323</v>
+        <v>6.732300000000001</v>
       </c>
       <c r="L27" t="n">
         <v>3.0475</v>
       </c>
       <c r="M27" t="n">
-        <v>9.2233</v>
+        <v>9.223300000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8983</v>
+        <v>4.898300000000001</v>
       </c>
       <c r="O27" t="n">
         <v>4.325</v>
@@ -2560,22 +2560,22 @@
         <v>17.4095</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.416999999999999</v>
+        <v>-6.135</v>
       </c>
       <c r="T27" t="n">
         <v>-1.0254</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.3916</v>
+        <v>-5.109599999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.5682</v>
+        <v>-1.568199999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>7.6747</v>
+        <v>7.674700000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.242800000000001</v>
+        <v>-9.242799999999999</v>
       </c>
     </row>
   </sheetData>
